--- a/Work_Log/Kevin_Hours_Log.xlsx
+++ b/Work_Log/Kevin_Hours_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\K_Documents\CEN4908C\Senior_Design_TI_Project\Work_Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D138FB0-0EF2-439A-B2C0-03766087552C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC57F05-5B8D-477B-A944-AB4F90F604BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
   <si>
     <t>Kevin Su Senior Design Work Log</t>
   </si>
@@ -114,6 +114,18 @@
   </si>
   <si>
     <t>Added GPIO for power and data along with pull up resistors.</t>
+  </si>
+  <si>
+    <t>Added voltage/buck converters to convert 5V to 1.8V, 1.2V, and 3.3V and removed unnecessary logic ICs.</t>
+  </si>
+  <si>
+    <t>Researched possible UART to USB IC for our PCB and USB ports.</t>
+  </si>
+  <si>
+    <t>Added UART to USB IC and USB ports to schematic for data and power delivery.</t>
+  </si>
+  <si>
+    <t>Added voltage switch IC, fixed connection errors, and added subheadings for clarification.</t>
   </si>
 </sst>
 </file>
@@ -527,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815A0D-EF96-486C-AACC-708D8CEA56AE}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.6328125" customWidth="1"/>
@@ -961,6 +973,86 @@
         <v>25</v>
       </c>
     </row>
+    <row r="23" spans="2:7" ht="64" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="3">
+        <v>46062</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="3">
+        <v>46064</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0.5625</v>
+      </c>
+      <c r="F24" s="5">
+        <v>6.25E-2</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="3">
+        <v>46065</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0.1875</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="3">
+        <v>46066</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="F26" s="5">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Work_Log/Kevin_Hours_Log.xlsx
+++ b/Work_Log/Kevin_Hours_Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\K_Documents\CEN4908C\Senior_Design_TI_Project\Work_Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC57F05-5B8D-477B-A944-AB4F90F604BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AE86FC-3396-467B-955C-5F6944B25669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="8170" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
   <si>
     <t>Kevin Su Senior Design Work Log</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>Added voltage switch IC, fixed connection errors, and added subheadings for clarification.</t>
+  </si>
+  <si>
+    <t>Assistem with data collection and ML model improvement suggestions.</t>
   </si>
 </sst>
 </file>
@@ -539,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815A0D-EF96-486C-AACC-708D8CEA56AE}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.6328125" customWidth="1"/>
@@ -1053,6 +1056,26 @@
         <v>29</v>
       </c>
     </row>
+    <row r="27" spans="2:7" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="3">
+        <v>46076</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F27" s="5">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Work_Log/Kevin_Hours_Log.xlsx
+++ b/Work_Log/Kevin_Hours_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\K_Documents\CEN4908C\Senior_Design_TI_Project\Work_Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AE86FC-3396-467B-955C-5F6944B25669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52CB9B9-82EC-4333-A4F1-74F11DD982F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="8170" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
   <si>
     <t>Kevin Su Senior Design Work Log</t>
   </si>
@@ -129,6 +129,15 @@
   </si>
   <si>
     <t>Assistem with data collection and ML model improvement suggestions.</t>
+  </si>
+  <si>
+    <t>Began redesigning PCB schematic for a Raspberry PI 4 backpack/peripheral.</t>
+  </si>
+  <si>
+    <t>Completed PCB schematic redesign for a Raspberry PI 4 backpack/peripheral.</t>
+  </si>
+  <si>
+    <t>Fixed wiring issues identified by Altium tool.</t>
   </si>
 </sst>
 </file>
@@ -542,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815A0D-EF96-486C-AACC-708D8CEA56AE}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.6328125" customWidth="1"/>
@@ -1067,13 +1076,73 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="E27" s="4">
-        <v>0.79166666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="F27" s="5">
-        <v>8.3333333333333329E-2</v>
+        <v>0.10416666666666667</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="3">
+        <v>46084</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E28" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="F28" s="5">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="3">
+        <v>46085</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0.65625</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F29" s="5">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="3">
+        <v>46085</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F30" s="5">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Work_Log/Kevin_Hours_Log.xlsx
+++ b/Work_Log/Kevin_Hours_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\K_Documents\CEN4908C\Senior_Design_TI_Project\Work_Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52CB9B9-82EC-4333-A4F1-74F11DD982F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FB9D77-DA80-4934-ADEE-A372EF7C3C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="8170" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="8170" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
   <si>
     <t>Kevin Su Senior Design Work Log</t>
   </si>
@@ -138,6 +138,15 @@
   </si>
   <si>
     <t>Fixed wiring issues identified by Altium tool.</t>
+  </si>
+  <si>
+    <t>Began placement of PCB components.</t>
+  </si>
+  <si>
+    <t>Worked on placing PCB components.</t>
+  </si>
+  <si>
+    <t>Completed PCB component placement and began routing.</t>
   </si>
 </sst>
 </file>
@@ -551,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815A0D-EF96-486C-AACC-708D8CEA56AE}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.6328125" customWidth="1"/>
@@ -1145,6 +1154,66 @@
         <v>33</v>
       </c>
     </row>
+    <row r="31" spans="2:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="3">
+        <v>46097</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="E31" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F31" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="3">
+        <v>46098</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="F32" s="5">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="3">
+        <v>46099</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="E33" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="F33" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Work_Log/Kevin_Hours_Log.xlsx
+++ b/Work_Log/Kevin_Hours_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\K_Documents\CEN4908C\Senior_Design_TI_Project\Work_Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FB9D77-DA80-4934-ADEE-A372EF7C3C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778D0DA3-9E43-4435-BEF1-7EE893263D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="8170" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="43">
   <si>
     <t>Kevin Su Senior Design Work Log</t>
   </si>
@@ -147,6 +147,24 @@
   </si>
   <si>
     <t>Completed PCB component placement and began routing.</t>
+  </si>
+  <si>
+    <t>Worked on PCB power, signal, and GND routing for a 2 layer board.</t>
+  </si>
+  <si>
+    <t>Worked on PCB power, signal, and GND routing for a 2 layer board. Ran into a roadblock running into routing conflicts.</t>
+  </si>
+  <si>
+    <t>Restarted PCB design for a 4 layer design. Did research on best methods of power distribution, thermal dissapation, and GND plane.</t>
+  </si>
+  <si>
+    <t>Continuted working PCB design for a 4 layer design. Began routing power and other netlist signals.</t>
+  </si>
+  <si>
+    <t>Continuted working PCB design for a 4 layer design. Continued routing netlist signals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuted working PCB design for a 4 layer design. Continued routing netlist signals. Created GND plane. </t>
   </si>
 </sst>
 </file>
@@ -560,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815A0D-EF96-486C-AACC-708D8CEA56AE}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.6328125" customWidth="1"/>
@@ -1214,6 +1232,126 @@
         <v>36</v>
       </c>
     </row>
+    <row r="34" spans="2:7" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="3">
+        <v>46100</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F34" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="64" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="3">
+        <v>46101</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F35" s="5">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="64" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="3">
+        <v>46102</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="F36" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="3">
+        <v>46103</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E37" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="F37" s="5">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="3">
+        <v>46104</v>
+      </c>
+      <c r="D38" s="4">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F38" s="5">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="3">
+        <v>46105</v>
+      </c>
+      <c r="D39" s="4">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F39" s="5">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Work_Log/Kevin_Hours_Log.xlsx
+++ b/Work_Log/Kevin_Hours_Log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\K_Documents\CEN4908C\Senior_Design_TI_Project\Work_Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778D0DA3-9E43-4435-BEF1-7EE893263D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D39A5B-D954-48EF-9CCB-5707CBF51F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
   </bookViews>
@@ -33,6 +33,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -259,6 +281,64 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>13</v>
+    <v>24</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -578,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815A0D-EF96-486C-AACC-708D8CEA56AE}">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.6328125" customWidth="1"/>
@@ -1212,7 +1292,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B33" s="2" t="s">
         <v>7</v>
       </c>
@@ -1232,7 +1312,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:9" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="2" t="s">
         <v>7</v>
       </c>
@@ -1252,7 +1332,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="64" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:9" ht="64" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="2" t="s">
         <v>7</v>
       </c>
@@ -1272,7 +1352,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="64" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:9" ht="64" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="2" t="s">
         <v>7</v>
       </c>
@@ -1292,7 +1372,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:9" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="2" t="s">
         <v>7</v>
       </c>
@@ -1312,7 +1392,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:9" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
         <v>7</v>
       </c>
@@ -1332,7 +1412,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:9" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
         <v>7</v>
       </c>
@@ -1350,6 +1430,12 @@
       </c>
       <c r="G39" s="2" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="I40" t="e" vm="1">
+        <f>_xleta.SUM</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>

--- a/Work_Log/Kevin_Hours_Log.xlsx
+++ b/Work_Log/Kevin_Hours_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\K_Documents\CEN4908C\Senior_Design_TI_Project\Work_Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D39A5B-D954-48EF-9CCB-5707CBF51F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660654F4-E0CD-464C-B752-ACC182AAE622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="46">
   <si>
     <t>Kevin Su Senior Design Work Log</t>
   </si>
@@ -187,6 +187,15 @@
   </si>
   <si>
     <t xml:space="preserve">Continuted working PCB design for a 4 layer design. Continued routing netlist signals. Created GND plane. </t>
+  </si>
+  <si>
+    <t>Completed 4 Layer PCB for review.</t>
+  </si>
+  <si>
+    <t>6:45:00PM</t>
+  </si>
+  <si>
+    <t>Completed code for SPI to transmit data from mmWaveradar.</t>
   </si>
 </sst>
 </file>
@@ -658,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815A0D-EF96-486C-AACC-708D8CEA56AE}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.6328125" customWidth="1"/>
@@ -1432,10 +1441,48 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="3">
+        <v>46107</v>
+      </c>
+      <c r="D40" s="4">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="F40" s="5">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="I40" t="e" vm="1">
         <f>_xleta.SUM</f>
         <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="3">
+        <v>46119</v>
+      </c>
+      <c r="D41" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="5">
+        <v>0.19791666666666666</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Work_Log/Kevin_Hours_Log.xlsx
+++ b/Work_Log/Kevin_Hours_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\K_Documents\CEN4908C\Senior_Design_TI_Project\Work_Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660654F4-E0CD-464C-B752-ACC182AAE622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD97889-4CDF-4EF6-BC7F-93843467038D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="47">
   <si>
     <t>Kevin Su Senior Design Work Log</t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>Completed code for SPI to transmit data from mmWaveradar.</t>
+  </si>
+  <si>
+    <t>Found new 3D models for PCB components and began redesiging to align with TI standards.</t>
   </si>
 </sst>
 </file>
@@ -258,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -275,6 +278,7 @@
     <xf numFmtId="21" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -667,13 +671,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815A0D-EF96-486C-AACC-708D8CEA56AE}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.6328125" customWidth="1"/>
     <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.6328125" customWidth="1"/>
+    <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1485,6 +1491,32 @@
         <v>45</v>
       </c>
     </row>
+    <row r="42" spans="2:9" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="3">
+        <v>46119</v>
+      </c>
+      <c r="D42" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="I43" s="6">
+        <f>SUM(F3:F42)</f>
+        <v>7.1097222222222243</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Work_Log/Kevin_Hours_Log.xlsx
+++ b/Work_Log/Kevin_Hours_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\K_Documents\CEN4908C\Senior_Design_TI_Project\Work_Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660654F4-E0CD-464C-B752-ACC182AAE622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0CFAEC-B4F5-4E77-9461-2B3D71CC2812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="15730" windowHeight="8830" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="49">
   <si>
     <t>Kevin Su Senior Design Work Log</t>
   </si>
@@ -196,6 +196,15 @@
   </si>
   <si>
     <t>Completed code for SPI to transmit data from mmWaveradar.</t>
+  </si>
+  <si>
+    <t>Found new 3D models for PCB components and began redesiging to align with TI standards.</t>
+  </si>
+  <si>
+    <t>Assisted team with data collection for ML classification model.</t>
+  </si>
+  <si>
+    <t>Assisted team with system integration for final presentation.</t>
   </si>
 </sst>
 </file>
@@ -258,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -275,6 +284,7 @@
     <xf numFmtId="21" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -667,13 +677,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815A0D-EF96-486C-AACC-708D8CEA56AE}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.6328125" customWidth="1"/>
     <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.6328125" customWidth="1"/>
+    <col min="8" max="8" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1485,6 +1496,72 @@
         <v>45</v>
       </c>
     </row>
+    <row r="42" spans="2:9" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="3">
+        <v>46122</v>
+      </c>
+      <c r="D42" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F42" s="5">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="3">
+        <v>46126</v>
+      </c>
+      <c r="D43" s="4">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F43" s="5">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="3">
+        <v>46127</v>
+      </c>
+      <c r="D44" s="4">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="F44" s="5">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="H45" s="6">
+        <f>SUM(F3:F44)</f>
+        <v>7.4013888888888903</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Work_Log/Kevin_Hours_Log.xlsx
+++ b/Work_Log/Kevin_Hours_Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\K_Documents\CEN4908C\Senior_Design_TI_Project\Work_Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0CFAEC-B4F5-4E77-9461-2B3D71CC2812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F5E58D-7F7B-4759-B42F-681B0B80C450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="15730" windowHeight="8830" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{1E1DE2E1-E43F-4C7B-805F-E7F882405594}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -150,9 +150,6 @@
     <t>Added voltage switch IC, fixed connection errors, and added subheadings for clarification.</t>
   </si>
   <si>
-    <t>Assistem with data collection and ML model improvement suggestions.</t>
-  </si>
-  <si>
     <t>Began redesigning PCB schematic for a Raspberry PI 4 backpack/peripheral.</t>
   </si>
   <si>
@@ -205,6 +202,9 @@
   </si>
   <si>
     <t>Assisted team with system integration for final presentation.</t>
+  </si>
+  <si>
+    <t>Assisted with data collection and ML model improvement suggestions.</t>
   </si>
 </sst>
 </file>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
@@ -732,7 +732,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -752,7 +752,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
@@ -772,7 +772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="176.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
@@ -792,7 +792,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="214" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="64" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
@@ -812,7 +812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="239" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="76.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
@@ -832,7 +832,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="226.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="64" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
@@ -852,7 +852,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="251.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" ht="76.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>0.10416666666666667</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="39" thickBot="1" x14ac:dyDescent="0.4">
@@ -1229,7 +1229,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="39" thickBot="1" x14ac:dyDescent="0.4">
@@ -1249,7 +1249,7 @@
         <v>5.2083333333333336E-2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1269,7 +1269,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1289,7 +1289,7 @@
         <v>0.125</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1309,7 +1309,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1329,7 +1329,7 @@
         <v>0.25</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="39" thickBot="1" x14ac:dyDescent="0.4">
@@ -1349,7 +1349,7 @@
         <v>0.25</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="64" thickBot="1" x14ac:dyDescent="0.4">
@@ -1369,7 +1369,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="64" thickBot="1" x14ac:dyDescent="0.4">
@@ -1389,7 +1389,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1409,7 +1409,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1429,7 +1429,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1449,7 +1449,7 @@
         <v>0.22916666666666666</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1469,7 +1469,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I40" t="e" vm="1">
         <f>_xleta.SUM</f>
@@ -1487,13 +1487,13 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F41" s="5">
         <v>0.19791666666666666</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1513,7 +1513,7 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="39" thickBot="1" x14ac:dyDescent="0.4">
@@ -1533,7 +1533,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="2:9" ht="39" thickBot="1" x14ac:dyDescent="0.4">
@@ -1553,7 +1553,7 @@
         <v>0.20833333333333334</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.35">
